--- a/data/performance/daily/signal_list_2026-05-19.xlsx
+++ b/data/performance/daily/signal_list_2026-05-19.xlsx
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 31.9%  (22W / 47L of 69 evaluated)</t>
+          <t>Win Rate: 34.8%  (24W / 45L of 69 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1360</v>
+        <v>1400</v>
       </c>
       <c r="D5" t="n">
         <v>1390</v>
@@ -553,14 +553,14 @@
         <v>1400</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.21</v>
+        <v>-0.71</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="G6" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -642,7 +642,7 @@
       <c r="G7" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -684,7 +684,7 @@
       <c r="G8" s="4" t="n">
         <v>-1.16</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -726,7 +726,7 @@
       <c r="G9" s="4" t="n">
         <v>7.48</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D10" t="n">
         <v>202</v>
@@ -763,14 +763,14 @@
         <v>212</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>-0.98</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -810,7 +810,7 @@
       <c r="G11" s="4" t="n">
         <v>-0.65</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1660</v>
+        <v>1655</v>
       </c>
       <c r="D12" t="n">
         <v>1645</v>
@@ -847,12 +847,12 @@
         <v>1670</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+        <v>-0.6</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2190</v>
+        <v>2240</v>
       </c>
       <c r="D13" t="n">
         <v>2300</v>
@@ -889,12 +889,12 @@
         <v>2330</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.39</v>
+        <v>4.02</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
+        <v>2.68</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -936,7 +936,7 @@
       <c r="G14" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -978,7 +978,7 @@
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1020,7 +1020,7 @@
       <c r="G16" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="D17" t="n">
         <v>2230</v>
@@ -1057,12 +1057,12 @@
         <v>2410</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.42</v>
+        <v>1.26</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.08</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+        <v>-6.3</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1190</v>
+        <v>1240</v>
       </c>
       <c r="D18" t="n">
         <v>1225</v>
@@ -1099,14 +1099,14 @@
         <v>1310</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.08</v>
+        <v>5.65</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.94</v>
+        <v>-1.21</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17000</v>
+        <v>16800</v>
       </c>
       <c r="D19" t="n">
         <v>16350</v>
@@ -1141,12 +1141,12 @@
         <v>17975</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.74</v>
+        <v>6.99</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
+        <v>-2.68</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D20" t="n">
         <v>113</v>
@@ -1183,12 +1183,12 @@
         <v>120</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.35</v>
+        <v>-9.09</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+        <v>-14.39</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1230,7 +1230,7 @@
       <c r="G21" s="4" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2180</v>
+        <v>2220</v>
       </c>
       <c r="D22" t="n">
         <v>2150</v>
@@ -1267,12 +1267,12 @@
         <v>2250</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.21</v>
+        <v>1.35</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+        <v>-3.15</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="D23" t="n">
         <v>505</v>
@@ -1309,12 +1309,12 @@
         <v>550</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-7.34</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+        <v>-8.18</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1356,7 +1356,7 @@
       <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="D25" t="n">
         <v>1000</v>
@@ -1393,14 +1393,14 @@
         <v>1005</v>
       </c>
       <c r="F25" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D26" t="n">
         <v>250</v>
@@ -1435,12 +1435,12 @@
         <v>256</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.4</v>
+        <v>0.79</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
+        <v>-1.57</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1482,7 +1482,7 @@
       <c r="G27" s="4" t="n">
         <v>-2.8</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" t="n">
         <v>68</v>
@@ -1519,12 +1519,12 @@
         <v>70</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.94</v>
+        <v>1.45</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+        <v>-1.45</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D29" t="n">
         <v>204</v>
@@ -1561,14 +1561,14 @@
         <v>216</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.88</v>
+        <v>8</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
         <v>78</v>
@@ -1603,12 +1603,12 @@
         <v>78</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D31" t="n">
         <v>426</v>
@@ -1645,12 +1645,12 @@
         <v>430</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.26</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.23</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>705.8</v>
+        <v>760</v>
       </c>
       <c r="D32" t="n">
         <v>710.47</v>
@@ -1687,14 +1687,14 @@
         <v>724.5</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.65</v>
+        <v>-4.67</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.66</v>
+        <v>-6.52</v>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2640</v>
+        <v>2600</v>
       </c>
       <c r="D33" t="n">
         <v>2630</v>
@@ -1729,14 +1729,14 @@
         <v>2640</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.38</v>
+        <v>1.15</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D34" t="n">
         <v>128</v>
@@ -1771,12 +1771,12 @@
         <v>148</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>24.37</v>
+        <v>23.33</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
+        <v>6.67</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>770</v>
+        <v>735</v>
       </c>
       <c r="D35" t="n">
         <v>810</v>
@@ -1813,12 +1813,12 @@
         <v>815</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.84</v>
+        <v>10.88</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
+        <v>10.2</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1860,7 +1860,7 @@
       <c r="G36" s="4" t="n">
         <v>19.75</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>502</v>
+        <v>555</v>
       </c>
       <c r="D37" t="n">
         <v>502</v>
@@ -1897,12 +1897,12 @@
         <v>502</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D38" t="n">
         <v>100</v>
@@ -1939,12 +1939,12 @@
         <v>105</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3.96</v>
+        <v>-2.78</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
+        <v>-7.41</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1986,7 +1986,7 @@
       <c r="G39" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" t="n">
         <v>79</v>
@@ -2023,12 +2023,12 @@
         <v>86</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2.38</v>
+        <v>3.61</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-5.95</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
+        <v>-4.82</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="D41" t="n">
         <v>1955</v>
@@ -2065,12 +2065,12 @@
         <v>1955</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+        <v>0.51</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -2112,7 +2112,7 @@
       <c r="G42" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D43" t="n">
         <v>161</v>
@@ -2149,12 +2149,12 @@
         <v>180</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5.88</v>
+        <v>7.14</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-5.29</v>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
+        <v>-4.17</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D44" t="n">
         <v>326</v>
@@ -2191,12 +2191,12 @@
         <v>338</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1.81</v>
+        <v>3.68</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>820</v>
+        <v>855</v>
       </c>
       <c r="D45" t="n">
         <v>800</v>
@@ -2233,12 +2233,12 @@
         <v>825</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.61</v>
+        <v>-3.51</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
+        <v>-6.43</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D46" t="n">
         <v>44</v>
@@ -2275,14 +2275,14 @@
         <v>44</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D47" t="n">
         <v>218</v>
@@ -2317,12 +2317,12 @@
         <v>232</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-6.03</v>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
+        <v>-6.84</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3420</v>
+        <v>3380</v>
       </c>
       <c r="D48" t="n">
         <v>3390</v>
@@ -2359,14 +2359,14 @@
         <v>3570</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4.39</v>
+        <v>5.62</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.88</v>
+        <v>0.3</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D49" t="n">
         <v>88</v>
@@ -2401,12 +2401,12 @@
         <v>92</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3.37</v>
+        <v>4.55</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2448,7 +2448,7 @@
       <c r="G50" s="4" t="n">
         <v>-2.82</v>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="D51" t="n">
         <v>990</v>
@@ -2485,12 +2485,12 @@
         <v>1005</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2532,7 +2532,7 @@
       <c r="G52" s="4" t="n">
         <v>-6.73</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D53" t="n">
         <v>101</v>
@@ -2569,14 +2569,14 @@
         <v>105</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2.94</v>
+        <v>6.06</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-0.98</v>
+        <v>2.02</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D54" t="n">
         <v>412</v>
@@ -2611,12 +2611,12 @@
         <v>416</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.48</v>
+        <v>0.97</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D55" t="n">
         <v>43</v>
@@ -2653,12 +2653,12 @@
         <v>45</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0</v>
+        <v>-4.26</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
+        <v>-8.51</v>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1470</v>
+        <v>1530</v>
       </c>
       <c r="D56" t="n">
         <v>1425</v>
@@ -2695,12 +2695,12 @@
         <v>1510</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2.72</v>
+        <v>-1.31</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-3.06</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
+        <v>-6.86</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2742,7 +2742,7 @@
       <c r="G57" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D58" t="n">
         <v>380</v>
@@ -2779,12 +2779,12 @@
         <v>380</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
+        <v>2.7</v>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -2826,7 +2826,7 @@
       <c r="G59" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D60" t="n">
         <v>150</v>
@@ -2863,12 +2863,12 @@
         <v>158</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-3.23</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
+        <v>-5.06</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2910,7 +2910,7 @@
       <c r="G61" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D62" t="n">
         <v>72</v>
@@ -2947,12 +2947,12 @@
         <v>75</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1.35</v>
+        <v>2.74</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
+        <v>-1.37</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D63" t="n">
         <v>153</v>
@@ -2989,12 +2989,12 @@
         <v>156</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
+        <v>-1.92</v>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3036,7 +3036,7 @@
       <c r="G64" s="4" t="n">
         <v>10.09</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D65" t="n">
         <v>162</v>
@@ -3073,12 +3073,12 @@
         <v>174</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-5.81</v>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
+        <v>-5.26</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D66" t="n">
         <v>500</v>
@@ -3115,12 +3115,12 @@
         <v>525</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
+        <v>-2.91</v>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D67" t="n">
         <v>344</v>
@@ -3157,12 +3157,12 @@
         <v>350</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>8.02</v>
+        <v>6.06</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
+        <v>4.24</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D68" t="n">
         <v>396</v>
@@ -3199,12 +3199,12 @@
         <v>540</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>14.89</v>
+        <v>16.38</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-15.74</v>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
+        <v>-14.66</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D69" t="n">
         <v>70</v>
@@ -3241,12 +3241,12 @@
         <v>74</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>4.23</v>
+        <v>1.37</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
+        <v>-4.11</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3274,7 +3274,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="D70" t="n">
         <v>418</v>
@@ -3283,12 +3283,12 @@
         <v>478</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>4.37</v>
+        <v>10.65</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-8.73</v>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
+        <v>-3.24</v>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D71" t="n">
         <v>168</v>
@@ -3325,12 +3325,12 @@
         <v>176</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
+        <v>-3.45</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -3372,7 +3372,7 @@
       <c r="G72" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -3414,7 +3414,7 @@
       <c r="G73" s="4" t="n">
         <v>5.13</v>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-19.xlsx
+++ b/data/performance/daily/signal_list_2026-05-19.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-19.xlsx
+++ b/data/performance/daily/signal_list_2026-05-19.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-19.xlsx
+++ b/data/performance/daily/signal_list_2026-05-19.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -602,15 +613,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -644,15 +660,20 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -686,15 +707,20 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -770,15 +801,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -812,15 +848,20 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -854,15 +895,20 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -894,17 +940,22 @@
       <c r="G13" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -938,15 +989,20 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,15 +1036,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1022,15 +1083,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1064,15 +1130,20 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1106,15 +1177,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1146,17 +1222,22 @@
       <c r="G19" s="4" t="n">
         <v>-1.94</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1190,15 +1271,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1230,17 +1316,22 @@
       <c r="G21" s="4" t="n">
         <v>-13.53</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1274,15 +1365,20 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1314,17 +1410,22 @@
       <c r="G23" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,17 +1457,22 @@
       <c r="G24" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1400,15 +1506,20 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1442,15 +1553,20 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1484,15 +1600,20 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1568,15 +1694,20 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1608,17 +1739,22 @@
       <c r="G30" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1652,15 +1788,20 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1694,15 +1835,20 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1736,15 +1882,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1776,17 +1927,22 @@
       <c r="G34" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1820,15 +1976,20 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1845,7 +2006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1855,9 +2016,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1887,7 +2049,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1912,15 +2074,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-19.xlsx
+++ b/data/performance/daily/signal_list_2026-05-19.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>2630</v>
       </c>
       <c r="D5" t="n">
+        <v>2670</v>
+      </c>
+      <c r="E5" t="n">
         <v>2580</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2670</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>780</v>
       </c>
       <c r="D6" t="n">
+        <v>780</v>
+      </c>
+      <c r="E6" t="n">
         <v>765</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>790</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.28</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>2310</v>
       </c>
       <c r="D7" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E7" t="n">
         <v>2240</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2460</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>6.49</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-3.03</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>342</v>
       </c>
       <c r="D8" t="n">
+        <v>344</v>
+      </c>
+      <c r="E8" t="n">
         <v>338</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>350</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>2.34</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-1.17</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>1600</v>
       </c>
       <c r="D9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E9" t="n">
         <v>1590</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1600</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>154</v>
       </c>
       <c r="D10" t="n">
+        <v>154</v>
+      </c>
+      <c r="E10" t="n">
         <v>151</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>156</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-1.95</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -838,30 +862,33 @@
         <v>2380</v>
       </c>
       <c r="E11" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F11" t="n">
         <v>2390</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>1200</v>
       </c>
       <c r="D12" t="n">
+        <v>1215</v>
+      </c>
+      <c r="E12" t="n">
         <v>1175</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1225</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>2.08</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-2.08</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>2890</v>
       </c>
       <c r="D13" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E13" t="n">
         <v>3130</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>3600</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>24.57</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>1485</v>
       </c>
       <c r="D14" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E14" t="n">
         <v>1480</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1505</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-0.34</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>5925</v>
       </c>
       <c r="D15" t="n">
+        <v>5900</v>
+      </c>
+      <c r="E15" t="n">
         <v>5925</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>6125</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>3.38</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>1005</v>
       </c>
       <c r="D16" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E16" t="n">
         <v>995</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1010</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>1720</v>
       </c>
       <c r="D17" t="n">
+        <v>1725</v>
+      </c>
+      <c r="E17" t="n">
         <v>1710</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1730</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>0.58</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-0.58</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>71</v>
       </c>
       <c r="D18" t="n">
+        <v>71</v>
+      </c>
+      <c r="E18" t="n">
         <v>69</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>73</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>2.82</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-2.82</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>775</v>
       </c>
       <c r="D19" t="n">
+        <v>775</v>
+      </c>
+      <c r="E19" t="n">
         <v>760</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>775</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-1.94</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>2670</v>
       </c>
       <c r="D20" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E20" t="n">
         <v>2600</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>2720</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>1.87</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-2.62</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>850</v>
       </c>
       <c r="D21" t="n">
+        <v>761.73</v>
+      </c>
+      <c r="E21" t="n">
         <v>735</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>761.73</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>-10.39</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-13.53</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>6575</v>
       </c>
       <c r="D22" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E22" t="n">
         <v>5950</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>6775</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>3.04</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-9.51</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>550</v>
       </c>
       <c r="D23" t="n">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="E23" t="n">
         <v>555</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>0.91</v>
+      <c r="F23" t="n">
+        <v>555</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H23" s="4" t="n">
+        <v>0.91</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>1800</v>
       </c>
       <c r="D24" t="n">
+        <v>1765</v>
+      </c>
+      <c r="E24" t="n">
         <v>1770</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>1795</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>-0.28</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>945</v>
       </c>
       <c r="D25" t="n">
+        <v>950</v>
+      </c>
+      <c r="E25" t="n">
         <v>855</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>950</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>0.53</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-9.52</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>240</v>
       </c>
       <c r="D26" t="n">
+        <v>252</v>
+      </c>
+      <c r="E26" t="n">
         <v>234</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>252</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>224</v>
       </c>
       <c r="D27" t="n">
+        <v>226</v>
+      </c>
+      <c r="E27" t="n">
         <v>218</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>234</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>4.46</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-2.68</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>420</v>
       </c>
       <c r="D28" t="n">
+        <v>422</v>
+      </c>
+      <c r="E28" t="n">
         <v>426</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>434</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>1.43</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>157</v>
       </c>
       <c r="D29" t="n">
+        <v>157</v>
+      </c>
+      <c r="E29" t="n">
         <v>156</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>159</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>985</v>
       </c>
       <c r="D30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E30" t="n">
         <v>1010</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>1030</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>4.57</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>2.54</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>220</v>
       </c>
       <c r="D31" t="n">
+        <v>220</v>
+      </c>
+      <c r="E31" t="n">
         <v>218</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>224</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>-0.91</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>80</v>
       </c>
       <c r="D32" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" t="n">
         <v>73</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>81</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-8.75</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>494</v>
       </c>
       <c r="D33" t="n">
+        <v>500</v>
+      </c>
+      <c r="E33" t="n">
         <v>432</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>500</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.21</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-12.55</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>7125</v>
       </c>
       <c r="D34" t="n">
-        <v>7175</v>
+        <v>7125</v>
       </c>
       <c r="E34" t="n">
         <v>7175</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>0.7</v>
+      <c r="F34" t="n">
+        <v>7175</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H34" s="4" t="n">
+        <v>0.7</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>2460</v>
       </c>
       <c r="D35" t="n">
+        <v>2460</v>
+      </c>
+      <c r="E35" t="n">
         <v>2330</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>2470</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>0.41</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-5.28</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2006,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2014,12 +2113,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2049,45 +2149,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
